--- a/target/test-classes/testdata/DailyJobs_UpdatedHourly.xlsx
+++ b/target/test-classes/testdata/DailyJobs_UpdatedHourly.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="254">
   <si>
     <t>Last Hour Job Search Results</t>
   </si>
@@ -639,6 +639,141 @@
   </si>
   <si>
     <t>https://www.linkedin.com/jobs/view/4435178385/</t>
+  </si>
+  <si>
+    <t>Senior Software Test Manager | Dyson | Dubai, Dubai, United Arab Emirates (On-site)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4399299020/</t>
+  </si>
+  <si>
+    <t>MEP QA/QC Engineer | Green Line Electromechanical L.L.C. | Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates (On-site)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4433723912/</t>
+  </si>
+  <si>
+    <t>Automation Test Engineer - QA (Remote) | Hire Feed | United Arab Emirates (Remote)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4436938466/</t>
+  </si>
+  <si>
+    <t>C# QA Lead - Remote | YO IT Consulting | United Arab Emirates (Remote)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4435714414/</t>
+  </si>
+  <si>
+    <t>Dotnet with Automation Testing (Playwright) | Virtusa | Dubai, Dubai, United Arab Emirates (Hybrid)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4433707874/</t>
+  </si>
+  <si>
+    <t>Finacle Automation Testing (Selenium/ Playwright) | Virtusa | Dubai, Dubai, United Arab Emirates (Hybrid)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4432708233/</t>
+  </si>
+  <si>
+    <t>Engineer - Civil (QA/QC) - PV | Larsen &amp; Toubro | United Arab Emirates (On-site)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4368620767/</t>
+  </si>
+  <si>
+    <t>Python QA Lead - Remote | YO IT Consulting | Dubai, Dubai, United Arab Emirates (Remote)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4435719378/</t>
+  </si>
+  <si>
+    <t>Go QA Lead - Remote | YO IT Consulting | United Arab Emirates (Remote)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4435709774/</t>
+  </si>
+  <si>
+    <t>Senior QA/QC Engineer - E&amp;I | Wood | Sharjah, Sharjah Emirate, United Arab Emirates (On-site)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4436753461/</t>
+  </si>
+  <si>
+    <t>Quality Assurance Engineer (Remote) | Hire Feed | United Arab Emirates (Remote)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4436938057/</t>
+  </si>
+  <si>
+    <t>Head Hostess - French Concept - Jumeirah Al Qasr | Jumeirah | Dubai, United Arab Emirates (On-site)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4433192493/</t>
+  </si>
+  <si>
+    <t>Quality Assurance Engineer | micro1 | EMEA (Remote)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4436730689/</t>
+  </si>
+  <si>
+    <t>Electrical QA/QC Engineer | CSCEC Middle East | Dubai, United Arab Emirates (On-site)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4433179890/</t>
+  </si>
+  <si>
+    <t>Manual &amp; Functional QA Testers - AI Experience Essential | Project Foundry Resourcing Services | EMEA (Remote)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4436727137/</t>
+  </si>
+  <si>
+    <t>Senior Engineer, Projects QA&amp;QC | ADNOC Group | Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates (On-site)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4436712427/</t>
+  </si>
+  <si>
+    <t>Manager, Quality &amp; Risk Management | ADNOC Group | Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates (On-site)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4436710565/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4433182385/</t>
+  </si>
+  <si>
+    <t>QA Automation Engineer | Sporty Group | EMEA (Remote)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4346013513/</t>
+  </si>
+  <si>
+    <t>Senior QA Automation Engineer (Remote) | Hire Feed | United Arab Emirates (Remote)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4436931443/</t>
+  </si>
+  <si>
+    <t>Manager | Audit | Audit &amp; Assurance | UAE FY27 | Deloitte | Abu Dhabi, Abu Dhabi Emirate, United Arab Emirates (On-site)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4389089317/</t>
+  </si>
+  <si>
+    <t>Job Description – QA Engineer (Manual &amp; Automation Testing) | Unicorn Lab | Dubai, Dubai, United Arab Emirates (On-site)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4433735887/</t>
+  </si>
+  <si>
+    <t>QA/QC Engineers- 5+ Years of Experience- High Rise Buildings Mandatory- Contracting Background | Auxilium | Dubai, Dubai, United Arab Emirates (On-site)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4433751438/</t>
   </si>
 </sst>
 </file>
@@ -683,7 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B116"/>
+  <dimension ref="A1:B141"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1587,6 +1722,200 @@
         <v>208</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="s" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="B118" t="s" s="0">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="B119" t="s" s="0">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="B120" t="s" s="0">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B121" t="s" s="0">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="0">
+        <v>217</v>
+      </c>
+      <c r="B122" t="s" s="0">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="0">
+        <v>219</v>
+      </c>
+      <c r="B123" t="s" s="0">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="0">
+        <v>221</v>
+      </c>
+      <c r="B124" t="s" s="0">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="B125" t="s" s="0">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="0">
+        <v>225</v>
+      </c>
+      <c r="B126" t="s" s="0">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="0">
+        <v>227</v>
+      </c>
+      <c r="B127" t="s" s="0">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="0">
+        <v>229</v>
+      </c>
+      <c r="B128" t="s" s="0">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="0">
+        <v>231</v>
+      </c>
+      <c r="B129" t="s" s="0">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="0">
+        <v>233</v>
+      </c>
+      <c r="B130" t="s" s="0">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="0">
+        <v>235</v>
+      </c>
+      <c r="B131" t="s" s="0">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="0">
+        <v>237</v>
+      </c>
+      <c r="B132" t="s" s="0">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="0">
+        <v>239</v>
+      </c>
+      <c r="B133" t="s" s="0">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="0">
+        <v>241</v>
+      </c>
+      <c r="B134" t="s" s="0">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B135" t="s" s="0">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="B136" t="s" s="0">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="0">
+        <v>246</v>
+      </c>
+      <c r="B137" t="s" s="0">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="0">
+        <v>248</v>
+      </c>
+      <c r="B139" t="s" s="0">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="B140" t="s" s="0">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="0">
+        <v>252</v>
+      </c>
+      <c r="B141" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
